--- a/data/ams_weekly_data/White_Mulberry/ads_report_week20.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week20.xlsx
@@ -4711,7 +4711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4774,16 +4774,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8785.5</v>
+        <v>8871</v>
       </c>
       <c r="E2" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F2" t="n">
-        <v>750.67</v>
+        <v>757.9767773673675</v>
       </c>
       <c r="G2" t="n">
-        <v>25255.075</v>
+        <v>25500.89967718328</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -4803,23 +4803,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8785.5</v>
+        <v>4436</v>
       </c>
       <c r="E3" t="n">
-        <v>320</v>
+        <v>162</v>
       </c>
       <c r="F3" t="n">
-        <v>750.67</v>
+        <v>378.9883886836838</v>
       </c>
       <c r="G3" t="n">
-        <v>25255.075</v>
+        <v>12750.44983859164</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4831,28 +4831,28 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3565.666666666667</v>
+        <v>4264</v>
       </c>
       <c r="E4" t="n">
-        <v>63.33333333333334</v>
+        <v>155</v>
       </c>
       <c r="F4" t="n">
-        <v>391.9066666666667</v>
+        <v>364.3748339489487</v>
       </c>
       <c r="G4" t="n">
-        <v>12919.48666666667</v>
+        <v>12258.80048422509</v>
       </c>
       <c r="H4" t="n">
-        <v>1.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4869,23 +4869,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3565.666666666667</v>
+        <v>10697</v>
       </c>
       <c r="E5" t="n">
-        <v>63.33333333333334</v>
+        <v>190</v>
       </c>
       <c r="F5" t="n">
-        <v>391.9066666666667</v>
+        <v>1175.72</v>
       </c>
       <c r="G5" t="n">
-        <v>12919.48666666667</v>
+        <v>38758.46</v>
       </c>
       <c r="H5" t="n">
-        <v>1.666666666666667</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4897,28 +4897,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3565.666666666667</v>
+        <v>7779</v>
       </c>
       <c r="E6" t="n">
-        <v>63.33333333333334</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>391.9066666666667</v>
+        <v>774.35</v>
       </c>
       <c r="G6" t="n">
-        <v>12919.48666666667</v>
+        <v>2414.41</v>
       </c>
       <c r="H6" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4930,28 +4930,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7779</v>
+        <v>11811</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="F7" t="n">
-        <v>774.35</v>
+        <v>1713.7</v>
       </c>
       <c r="G7" t="n">
-        <v>2414.41</v>
+        <v>4828.81</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4963,28 +4963,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11811</v>
+        <v>4609</v>
       </c>
       <c r="E8" t="n">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>1713.7</v>
+        <v>900.9342175220972</v>
       </c>
       <c r="G8" t="n">
-        <v>4828.81</v>
+        <v>2202.54</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -5001,25 +5001,58 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14642</v>
+        <v>4715</v>
       </c>
       <c r="E9" t="n">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>2862.26</v>
+        <v>921.7299786064923</v>
       </c>
       <c r="G9" t="n">
-        <v>6997.450000000001</v>
+        <v>2253.38</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5318</v>
+      </c>
+      <c r="E10" t="n">
+        <v>51</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1039.59580387141</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2541.53</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week20.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week20.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
